--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>131157730</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131159001</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>131157730</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131159001</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>131157730</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131159001</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>131157730</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131159001</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>131157730</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131159001</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1522,7 +1522,7 @@
         <v>131157730</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131159001</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,6 +1735,223 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131234957</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brattmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>714918</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7090576</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Torraka med flera bohål</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131159004</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brattmyran, Brattmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>714918</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7090576</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1953,6 +1953,1233 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131710413</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>715187</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7090801</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131710408</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>715048</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7090787</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131710404</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>715199</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7090915</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131710406</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>715075</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7090595</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131710414</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>715054</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7090707</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131710409</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>715049</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7090604</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131710415</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>715101</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7090876</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131710407</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>715168</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7090714</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131710410</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80365</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>715062</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7090696</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131710412</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>715237</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7090942</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131710405</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>714988</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7090688</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131710411</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tofskärrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>715229</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7090947</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131234957</v>
+        <v>131159004</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,35 +1749,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brattmyran, Ång</t>
+          <t>Brattmyran, Brattmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1814,21 +1806,26 @@
           <t>2026-02-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Torraka med flera bohål</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1848,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131159004</v>
+        <v>131234957</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,27 +1856,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brattmyran, Brattmyran, Ång</t>
+          <t>Brattmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1916,26 +1921,21 @@
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:31</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Torraka med flera bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -2372,10 +2372,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131710414</v>
+        <v>131710409</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,34 +2383,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715054</v>
+        <v>715049</v>
       </c>
       <c r="R17" t="n">
-        <v>7090707</v>
+        <v>7090604</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,6 +2451,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131710409</v>
+        <v>131710414</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,42 +2493,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715049</v>
+        <v>715054</v>
       </c>
       <c r="R18" t="n">
-        <v>7090604</v>
+        <v>7090707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,11 +2553,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>131157730</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131159001</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131159004</v>
+        <v>131234957</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,27 +1749,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brattmyran, Brattmyran, Ång</t>
+          <t>Brattmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1806,26 +1814,21 @@
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:31</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Torraka med flera bohål</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1845,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131234957</v>
+        <v>131159004</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,35 +1859,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brattmyran, Ång</t>
+          <t>Brattmyran, Brattmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1921,21 +1916,26 @@
           <t>2026-02-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Torraka med flera bohål</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131710413</v>
+        <v>131710408</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,34 +1966,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715187</v>
+        <v>715048</v>
       </c>
       <c r="R13" t="n">
-        <v>7090801</v>
+        <v>7090787</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,6 +2034,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131710408</v>
+        <v>131710404</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>58058</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,21 +2076,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2085,7 +2098,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2095,10 +2108,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715048</v>
+        <v>715199</v>
       </c>
       <c r="R14" t="n">
-        <v>7090787</v>
+        <v>7090915</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,11 +2144,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131710404</v>
+        <v>131710413</v>
       </c>
       <c r="B15" t="n">
-        <v>58057</v>
+        <v>79261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,42 +2181,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715199</v>
+        <v>715187</v>
       </c>
       <c r="R15" t="n">
-        <v>7090915</v>
+        <v>7090801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
         <v>131710406</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131710409</v>
+        <v>131710414</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,42 +2383,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715049</v>
+        <v>715054</v>
       </c>
       <c r="R17" t="n">
-        <v>7090604</v>
+        <v>7090707</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,11 +2443,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131710414</v>
+        <v>131710409</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,34 +2480,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715054</v>
+        <v>715049</v>
       </c>
       <c r="R18" t="n">
-        <v>7090707</v>
+        <v>7090604</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,6 +2548,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,7 +2582,7 @@
         <v>131710415</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>131710407</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>131710410</v>
       </c>
       <c r="B21" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>131710412</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>131710405</v>
       </c>
       <c r="B23" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>131710411</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>131157730</v>
       </c>
       <c r="B9" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131159001</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>131234957</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>131159004</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131710408</v>
+        <v>131710413</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,42 +1966,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715048</v>
+        <v>715187</v>
       </c>
       <c r="R13" t="n">
-        <v>7090787</v>
+        <v>7090801</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,11 +2026,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,7 +2055,7 @@
         <v>131710404</v>
       </c>
       <c r="B14" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131710413</v>
+        <v>131710408</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,34 +2168,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715187</v>
+        <v>715048</v>
       </c>
       <c r="R15" t="n">
-        <v>7090801</v>
+        <v>7090787</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,6 +2236,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,7 +2270,7 @@
         <v>131710406</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131710414</v>
+        <v>131710409</v>
       </c>
       <c r="B17" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,34 +2383,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715054</v>
+        <v>715049</v>
       </c>
       <c r="R17" t="n">
-        <v>7090707</v>
+        <v>7090604</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,6 +2451,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131710409</v>
+        <v>131710414</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,42 +2493,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715049</v>
+        <v>715054</v>
       </c>
       <c r="R18" t="n">
-        <v>7090604</v>
+        <v>7090707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,11 +2553,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,7 +2582,7 @@
         <v>131710415</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>131710407</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>131710410</v>
       </c>
       <c r="B21" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>131710412</v>
       </c>
       <c r="B22" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>131710405</v>
       </c>
       <c r="B23" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>131710411</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131234957</v>
+        <v>131159004</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,35 +1749,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brattmyran, Ång</t>
+          <t>Brattmyran, Brattmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1814,21 +1806,26 @@
           <t>2026-02-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Torraka med flera bohål</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1848,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131159004</v>
+        <v>131234957</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,27 +1856,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brattmyran, Brattmyran, Ång</t>
+          <t>Brattmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1916,26 +1921,21 @@
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:31</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Torraka med flera bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131710413</v>
+        <v>131710404</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>58061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,34 +1966,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715187</v>
+        <v>715199</v>
       </c>
       <c r="R13" t="n">
-        <v>7090801</v>
+        <v>7090915</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131710404</v>
+        <v>131710413</v>
       </c>
       <c r="B14" t="n">
-        <v>58061</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,42 +2071,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715199</v>
+        <v>715187</v>
       </c>
       <c r="R14" t="n">
-        <v>7090915</v>
+        <v>7090801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1955,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131710408</v>
+        <v>131710413</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,42 +1966,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715048</v>
+        <v>715187</v>
       </c>
       <c r="R13" t="n">
-        <v>7090787</v>
+        <v>7090801</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,11 +2026,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,7 +2055,7 @@
         <v>131710404</v>
       </c>
       <c r="B14" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131710413</v>
+        <v>131710408</v>
       </c>
       <c r="B15" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,34 +2168,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715187</v>
+        <v>715048</v>
       </c>
       <c r="R15" t="n">
-        <v>7090801</v>
+        <v>7090787</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,6 +2236,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2485,7 +2485,7 @@
         <v>131710414</v>
       </c>
       <c r="B18" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>131710415</v>
       </c>
       <c r="B19" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>131710410</v>
       </c>
       <c r="B21" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>131710412</v>
       </c>
       <c r="B22" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>131710405</v>
       </c>
       <c r="B23" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>131710411</v>
       </c>
       <c r="B24" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 6819-2026 artfynd.xlsx
+++ b/artfynd/A 6819-2026 artfynd.xlsx
@@ -1955,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131710413</v>
+        <v>131710404</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>58109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,34 +1966,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715187</v>
+        <v>715199</v>
       </c>
       <c r="R13" t="n">
-        <v>7090801</v>
+        <v>7090915</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131710404</v>
+        <v>131710413</v>
       </c>
       <c r="B14" t="n">
-        <v>58109</v>
+        <v>79317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,42 +2071,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tofskärrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715199</v>
+        <v>715187</v>
       </c>
       <c r="R14" t="n">
-        <v>7090915</v>
+        <v>7090801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
